--- a/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Datas/NumericValueLimit.xlsx
+++ b/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Datas/NumericValueLimit.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -304,12 +304,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -50314,7 +50314,10 @@
       <c r="XEZ3"/>
       <c r="XFA3"/>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
